--- a/data/trans_orig/P13_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38068</t>
+          <t>38144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672800</t>
+          <t>672982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687209</t>
+          <t>687365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664472</t>
+          <t>664639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>680839</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1344295</t>
+          <t>1344219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1364965</t>
+          <t>1364468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51482</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55486</t>
+          <t>58143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64392</t>
+          <t>64872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101029</t>
+          <t>103403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>910318</t>
+          <t>910390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>934038</t>
+          <t>934549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>912907</t>
+          <t>910250</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939045</t>
+          <t>937517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1829164</t>
+          <t>1826790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1865801</t>
+          <t>1865321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49711</t>
+          <t>49477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46623</t>
+          <t>45161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78461</t>
+          <t>75623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643548</t>
+          <t>644279</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664428</t>
+          <t>664601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634130</t>
+          <t>634364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657531</t>
+          <t>657171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1283889</t>
+          <t>1286727</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1315727</t>
+          <t>1317189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>43892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56395</t>
+          <t>56644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82475</t>
+          <t>82716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121128</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898432</t>
+          <t>898330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920931</t>
+          <t>921351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948878</t>
+          <t>949568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>982217</t>
+          <t>981968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1859706</t>
+          <t>1857389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898359</t>
+          <t>1898118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85961</t>
+          <t>86111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>140887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189635</t>
+          <t>192328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238296</t>
+          <t>237495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303755</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3151037</t>
+          <t>3148980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3190582</t>
+          <t>3190432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3189562</t>
+          <t>3186869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3242186</t>
+          <t>3238310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6351986</t>
+          <t>6354738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6417445</t>
+          <t>6418246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24309</t>
+          <t>24834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47158</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61562</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95772</t>
+          <t>95438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90874</t>
+          <t>89897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135405</t>
+          <t>132709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655346</t>
+          <t>652170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678195</t>
+          <t>677670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600343</t>
+          <t>600677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634553</t>
+          <t>634348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1263213</t>
+          <t>1265909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1307744</t>
+          <t>1308721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66234</t>
+          <t>66175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,82 +3038,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>83576</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67259</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>104593</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>133368</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>111256</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>156288</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83576</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68030</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>102119</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>133368</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>111037</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>158496</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>951713</t>
+          <t>951772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>982022</t>
+          <t>980708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,82 +3151,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>947589</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>926572</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>963906</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>89,86%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1915744</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1892824</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1937856</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>93,49%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>947589</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>929046</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>963135</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1915744</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1890616</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1938075</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44279</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51659</t>
+          <t>50700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85122</t>
+          <t>84080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79236</t>
+          <t>78477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117803</t>
+          <t>117719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>712397</t>
+          <t>713711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>736114</t>
+          <t>736399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690954</t>
+          <t>691996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>724417</t>
+          <t>725376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1414950</t>
+          <t>1415034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1453517</t>
+          <t>1454276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58637</t>
+          <t>58480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86924</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125303</t>
+          <t>127086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126207</t>
+          <t>125984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176135</t>
+          <t>174840</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888072</t>
+          <t>888229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914301</t>
+          <t>913477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>926598</t>
+          <t>924815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964977</t>
+          <t>964607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1822475</t>
+          <t>1823770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872403</t>
+          <t>1872626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135106</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188271</t>
+          <t>185836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296176</t>
+          <t>297009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>369679</t>
+          <t>369396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>444062</t>
+          <t>448149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>535778</t>
+          <t>534402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3235565</t>
+          <t>3238000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3288730</t>
+          <t>3289503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3185578</t>
+          <t>3185861</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3259081</t>
+          <t>3258248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6443315</t>
+          <t>6444691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6535031</t>
+          <t>6530944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37693</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>57941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87953</t>
+          <t>88245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637107</t>
+          <t>636692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657130</t>
+          <t>658135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610678</t>
+          <t>612999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638625</t>
+          <t>639503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1257787</t>
+          <t>1257495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1291755</t>
+          <t>1291295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38857</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58323</t>
+          <t>57758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92021</t>
+          <t>94109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>982601</t>
+          <t>981983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003859</t>
+          <t>1003196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>980326</t>
+          <t>979984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1008310</t>
+          <t>1009084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1971369</t>
+          <t>1969281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2005067</t>
+          <t>2005632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>53870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86970</t>
+          <t>85666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719617</t>
+          <t>717979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>741502</t>
+          <t>741334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>729207</t>
+          <t>729870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>754591</t>
+          <t>755640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1456322</t>
+          <t>1457626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1490610</t>
+          <t>1492689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49224</t>
+          <t>49167</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84664</t>
+          <t>84720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83281</t>
+          <t>84418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126679</t>
+          <t>125598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888343</t>
+          <t>888400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913007</t>
+          <t>911354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>958228</t>
+          <t>958172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>991080</t>
+          <t>992333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1853780</t>
+          <t>1854861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897178</t>
+          <t>1896041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97926</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>140779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167866</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223954</t>
+          <t>226190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280753</t>
+          <t>279351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>353544</t>
+          <t>353703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3253288</t>
+          <t>3252599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3295452</t>
+          <t>3296847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3315550</t>
+          <t>3313314</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3371638</t>
+          <t>3369504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6579337</t>
+          <t>6579178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6652128</t>
+          <t>6653530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73340</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101893</t>
+          <t>102933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>580752</t>
+          <t>579202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604138</t>
+          <t>604653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>615822</t>
+          <t>616534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634514</t>
+          <t>634148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1204540</t>
+          <t>1203500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1233093</t>
+          <t>1234463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83371</t>
+          <t>83880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67661</t>
+          <t>68651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129044</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1138326</t>
+          <t>1138311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1172360</t>
+          <t>1174094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>873441</t>
+          <t>872932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>899178</t>
+          <t>898117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2020632</t>
+          <t>2021256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2082015</t>
+          <t>2081025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67967</t>
+          <t>66962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>53641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104862</t>
+          <t>106905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655172</t>
+          <t>655098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678072</t>
+          <t>678359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>864984</t>
+          <t>865989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>908567</t>
+          <t>909972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1532769</t>
+          <t>1530726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1582936</t>
+          <t>1583990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41860</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69713</t>
+          <t>71769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>68159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101514</t>
+          <t>102166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120387</t>
+          <t>119257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162861</t>
+          <t>163004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855493</t>
+          <t>853437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883346</t>
+          <t>882429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>993418</t>
+          <t>992766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028165</t>
+          <t>1026773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857278</t>
+          <t>1857135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1899752</t>
+          <t>1900882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>130009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196052</t>
+          <t>196862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202910</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>280250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365723</t>
+          <t>361230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459618</t>
+          <t>459412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3260240</t>
+          <t>3259430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3331449</t>
+          <t>3326283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3376864</t>
+          <t>3377337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3454677</t>
+          <t>3453811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6654261</t>
+          <t>6654467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6748156</t>
+          <t>6752649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672982</t>
+          <t>673826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687365</t>
+          <t>687375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664639</t>
+          <t>666360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>680926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1344219</t>
+          <t>1343666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1364468</t>
+          <t>1364599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>54719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58143</t>
+          <t>56272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64872</t>
+          <t>65062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103403</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>910390</t>
+          <t>907081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>934549</t>
+          <t>933202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>910250</t>
+          <t>912121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>937517</t>
+          <t>938648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1826790</t>
+          <t>1830309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1865321</t>
+          <t>1865131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45161</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75623</t>
+          <t>77384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644279</t>
+          <t>644129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664601</t>
+          <t>664303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634364</t>
+          <t>634562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657171</t>
+          <t>657478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286727</t>
+          <t>1284966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317189</t>
+          <t>1315935</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>55414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89044</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82716</t>
+          <t>82287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123445</t>
+          <t>122676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898330</t>
+          <t>898663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921351</t>
+          <t>922165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>949568</t>
+          <t>950473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>981968</t>
+          <t>983198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857389</t>
+          <t>1858158</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898118</t>
+          <t>1898547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86111</t>
+          <t>84933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140887</t>
+          <t>140324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192328</t>
+          <t>190043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>235509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>302413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3148980</t>
+          <t>3149068</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3190432</t>
+          <t>3191610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3186869</t>
+          <t>3189154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3238310</t>
+          <t>3238873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6354738</t>
+          <t>6353328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6418246</t>
+          <t>6420232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24834</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50334</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95438</t>
+          <t>94319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89897</t>
+          <t>92192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132709</t>
+          <t>132423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652170</t>
+          <t>654666</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>677670</t>
+          <t>678649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600677</t>
+          <t>601796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634348</t>
+          <t>636155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1265909</t>
+          <t>1266195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1308721</t>
+          <t>1306426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66175</t>
+          <t>64222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67259</t>
+          <t>68181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>104009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111256</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156288</t>
+          <t>154905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>951772</t>
+          <t>953725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>980708</t>
+          <t>982982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926572</t>
+          <t>927156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>963906</t>
+          <t>962984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1892824</t>
+          <t>1894207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1937856</t>
+          <t>1937970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42965</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>52479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84080</t>
+          <t>84445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78477</t>
+          <t>76913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117719</t>
+          <t>118126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>713711</t>
+          <t>713313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>736399</t>
+          <t>736867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691996</t>
+          <t>691631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>725376</t>
+          <t>723597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1415034</t>
+          <t>1414627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1454276</t>
+          <t>1455840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>32839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58480</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>85500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127086</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>126642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174840</t>
+          <t>176221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888229</t>
+          <t>887009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913477</t>
+          <t>913870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>924815</t>
+          <t>925205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964607</t>
+          <t>966401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1823770</t>
+          <t>1822389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872626</t>
+          <t>1871968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>134333</t>
+          <t>135453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297009</t>
+          <t>299047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>369396</t>
+          <t>365052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>448149</t>
+          <t>443214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>534402</t>
+          <t>537191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3238000</t>
+          <t>3233077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3289503</t>
+          <t>3288383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3185861</t>
+          <t>3190205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3258248</t>
+          <t>3256210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6444691</t>
+          <t>6441902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6530944</t>
+          <t>6535879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>57145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54445</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88245</t>
+          <t>85045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636692</t>
+          <t>638256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>658135</t>
+          <t>657707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612999</t>
+          <t>613795</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>639503</t>
+          <t>639672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1257495</t>
+          <t>1260695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1291295</t>
+          <t>1292619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39475</t>
+          <t>40364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>62401</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>57144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94109</t>
+          <t>92099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981983</t>
+          <t>981094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003196</t>
+          <t>1002823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>979984</t>
+          <t>979531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1009084</t>
+          <t>1006895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1969281</t>
+          <t>1971291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2005632</t>
+          <t>2006246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28100</t>
+          <t>28033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>52687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85666</t>
+          <t>86348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717979</t>
+          <t>720155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>741334</t>
+          <t>741730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>729870</t>
+          <t>729946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>755640</t>
+          <t>755707</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1457626</t>
+          <t>1456944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1492689</t>
+          <t>1490605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>26068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>49404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50559</t>
+          <t>51142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84720</t>
+          <t>85589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84418</t>
+          <t>83348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125598</t>
+          <t>127573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888400</t>
+          <t>888163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>911354</t>
+          <t>911499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>958172</t>
+          <t>957303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992333</t>
+          <t>991750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854861</t>
+          <t>1852886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1896041</t>
+          <t>1897111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96531</t>
+          <t>96776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140779</t>
+          <t>141560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>226190</t>
+          <t>224144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279351</t>
+          <t>281018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>353703</t>
+          <t>352040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3252599</t>
+          <t>3251818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3296847</t>
+          <t>3296602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3313314</t>
+          <t>3315360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3369504</t>
+          <t>3370824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6579178</t>
+          <t>6580841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6653530</t>
+          <t>6651863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>31713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54339</t>
+          <t>57391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46653</t>
+          <t>50297</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56358</t>
+          <t>61633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86039</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71970</t>
+          <t>78596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102933</t>
+          <t>109986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>594156</t>
+          <t>646863</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>579202</t>
+          <t>631247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604653</t>
+          <t>656925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>626239</t>
+          <t>679781</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616534</t>
+          <t>668445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634148</t>
+          <t>689389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1220394</t>
+          <t>1326646</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1203500</t>
+          <t>1308731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1234463</t>
+          <t>1340121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633541</t>
+          <t>688638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633541</t>
+          <t>688638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633541</t>
+          <t>688638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>672892</t>
+          <t>730078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>672892</t>
+          <t>730078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>672892</t>
+          <t>730078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1306433</t>
+          <t>1418717</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1306433</t>
+          <t>1418717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1306433</t>
+          <t>1418717</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54553</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>76679</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>64392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83880</t>
+          <t>92997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>115481</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68651</t>
+          <t>98732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128420</t>
+          <t>134313</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1155973</t>
+          <t>1010115</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1138311</t>
+          <t>994978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1174094</t>
+          <t>1019990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>887195</t>
+          <t>992767</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>872932</t>
+          <t>976449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>898117</t>
+          <t>1005054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2043168</t>
+          <t>2002882</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2021256</t>
+          <t>1984050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2081025</t>
+          <t>2019631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956812</t>
+          <t>1069446</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956812</t>
+          <t>1069446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956812</t>
+          <t>1069446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149676</t>
+          <t>2118363</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149676</t>
+          <t>2118363</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149676</t>
+          <t>2118363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>55548</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>44416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>70513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>84949</t>
+          <t>102658</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53641</t>
+          <t>85951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106905</t>
+          <t>124396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>667777</t>
+          <t>755963</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655098</t>
+          <t>738541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678359</t>
+          <t>768444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>884906</t>
+          <t>756234</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>865989</t>
+          <t>741269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909972</t>
+          <t>767366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1552682</t>
+          <t>1512197</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1530726</t>
+          <t>1490459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1583990</t>
+          <t>1528904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932951</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932951</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932951</t>
+          <t>811782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637631</t>
+          <t>1614855</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637631</t>
+          <t>1614855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637631</t>
+          <t>1614855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54901</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71769</t>
+          <t>73255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85761</t>
+          <t>95626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>81722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102166</t>
+          <t>111570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>152391</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119257</t>
+          <t>132756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163004</t>
+          <t>174290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>870305</t>
+          <t>931696</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853437</t>
+          <t>915206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882429</t>
+          <t>944319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1009171</t>
+          <t>1023415</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>992766</t>
+          <t>1007471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026773</t>
+          <t>1037319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1879477</t>
+          <t>1955111</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857135</t>
+          <t>1933212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1900882</t>
+          <t>1974746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925206</t>
+          <t>988461</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925206</t>
+          <t>988461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925206</t>
+          <t>988461</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2020139</t>
+          <t>2107502</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2020139</t>
+          <t>2107502</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2020139</t>
+          <t>2107502</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130009</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196862</t>
+          <t>213718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>278150</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203776</t>
+          <t>253214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>280250</t>
+          <t>305625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>462601</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>361230</t>
+          <t>427953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459412</t>
+          <t>501471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3288211</t>
+          <t>3344637</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3259430</t>
+          <t>3315371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3326283</t>
+          <t>3368471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3407511</t>
+          <t>3452198</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3377337</t>
+          <t>3424723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3453811</t>
+          <t>3477134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6695722</t>
+          <t>6796837</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6654467</t>
+          <t>6757967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6752649</t>
+          <t>6831485</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
